--- a/products.xlsx
+++ b/products.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\aidesk\geminitnutrition\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3603972F-26B1-4702-804B-C40D56FC9551}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F509174B-1A4E-40DA-BE98-4F7FCE73F856}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,24 +27,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
   <si>
-    <t>列 A：品牌名</t>
-  </si>
-  <si>
-    <t>列 B：商品官方全称</t>
-  </si>
-  <si>
-    <t>列 C：搜索别名(逗号隔开)</t>
-  </si>
-  <si>
-    <t>列 D：每日建议服用几粒</t>
-  </si>
-  <si>
-    <t>列 E：包含的成分(对应表1中文名)</t>
-  </si>
-  <si>
-    <t>列 F：单粒原料投料量</t>
-  </si>
-  <si>
     <t>Swisse</t>
   </si>
   <si>
@@ -67,13 +49,140 @@
   </si>
   <si>
     <t>氨基葡萄糖</t>
+  </si>
+  <si>
+    <t>品牌名</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>商品官方全称</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>搜索别名</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>逗号隔开</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>每日建议服用几粒</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>包含的成分</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>对应表</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>中文名</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>单粒原料投料量</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -101,6 +210,22 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -122,12 +247,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
   </cellXfs>
@@ -413,63 +541,63 @@
   <dimension ref="A1:F3"/>
   <sheetFormatPr defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
   <sheetData>
-    <row r="1" spans="1:6" ht="55.5" x14ac:dyDescent="0.4">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
+    <row r="1" spans="1:6" ht="47.25" x14ac:dyDescent="0.4">
+      <c r="A1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="54" x14ac:dyDescent="0.4">
-      <c r="A2" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D2" s="2">
+      <c r="A2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F2" s="2">
+      <c r="D2" s="1">
+        <v>2</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F2" s="1">
         <v>150</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="40.5" x14ac:dyDescent="0.4">
-      <c r="A3" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D3" s="2">
+      <c r="A3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D3" s="1">
         <v>3</v>
       </c>
-      <c r="E3" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F3" s="2">
+      <c r="E3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F3" s="1">
         <v>500</v>
       </c>
     </row>
